--- a/data/trans_orig/IQ22A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias</t>
+          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias (tasa de respuesta: 93,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,57 +716,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,83</t>
+          <t>1,51; 4,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,88</t>
+          <t>1,92; 4,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,31</t>
+          <t>1,47; 2,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,93</t>
+          <t>1,72; 2,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,71</t>
+          <t>1,6; 2,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,62</t>
+          <t>1,63; 2,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,28</t>
+          <t>1,63; 3,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,08</t>
+          <t>1,61; 3,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,83</t>
+          <t>1,71; 2,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,05</t>
+          <t>1,84; 3,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,55</t>
+          <t>1,65; 2,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,5</t>
+          <t>1,13; 1,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,32</t>
+          <t>1,67; 3,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,13</t>
+          <t>1,62; 2,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,87</t>
+          <t>1,62; 4,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,91</t>
+          <t>1,39; 1,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,27</t>
+          <t>1,29; 2,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,94</t>
+          <t>1,36; 1,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,05</t>
+          <t>1,43; 3,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,68</t>
+          <t>1,32; 1,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,43</t>
+          <t>1,57; 2,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,94</t>
+          <t>1,54; 1,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,42</t>
+          <t>1,76; 3,46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,22 +996,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,17</t>
+          <t>1,24; 2,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,85</t>
+          <t>1,52; 2,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,41</t>
+          <t>1,14; 2,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,37</t>
+          <t>1,13; 2,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,7</t>
+          <t>1,15; 1,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,16</t>
+          <t>1,0; 2,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,71</t>
+          <t>1,2; 1,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,13</t>
+          <t>1,41; 2,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,1</t>
+          <t>1,09; 2,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,04</t>
+          <t>1,15; 2,12</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,86</t>
+          <t>1,22; 1,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,15</t>
+          <t>1,9; 4,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,29</t>
+          <t>1,62; 3,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,1</t>
+          <t>1,27; 3,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,63</t>
+          <t>1,37; 2,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,76</t>
+          <t>1,5; 2,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,13</t>
+          <t>1,84; 3,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,68</t>
+          <t>1,56; 4,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,13</t>
+          <t>1,41; 2,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,97</t>
+          <t>1,8; 3,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,85</t>
+          <t>1,88; 2,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,25</t>
+          <t>1,5; 3,2</t>
         </is>
       </c>
     </row>
@@ -1276,17 +1276,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,68</t>
+          <t>1,11; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,72</t>
+          <t>1,22; 1,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,85</t>
+          <t>1,0; 3,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,78</t>
+          <t>1,25; 2,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,55</t>
+          <t>1,58; 2,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1316,29 +1316,29 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,46</t>
+          <t>1,29; 2,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 1,97</t>
+          <t>1,44; 1,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,8</t>
+          <t>1,19; 2,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,91</t>
+          <t>1,0; 2,04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,56</t>
+          <t>1,0; 1,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,66</t>
+          <t>1,17; 1,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,14</t>
+          <t>1,38; 5,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,49 +1436,49 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,7</t>
+          <t>1,14; 1,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,4</t>
+          <t>1,03; 1,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,56</t>
+          <t>1,16; 3,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,39</t>
+          <t>1,29; 4,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,45</t>
+          <t>1,12; 1,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,45</t>
+          <t>1,13; 1,43</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,68</t>
+          <t>1,43; 4,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,17</t>
+          <t>1,18; 2,85</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1561,47 +1561,47 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,62</t>
+          <t>1,19; 1,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,16</t>
+          <t>1,24; 2,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,27</t>
+          <t>1,21; 2,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,98</t>
+          <t>1,31; 1,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,0</t>
+          <t>1,36; 2,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,72</t>
+          <t>1,18; 1,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,22</t>
+          <t>1,35; 2,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,72</t>
+          <t>1,3; 1,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,77</t>
+          <t>1,34; 1,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,94</t>
+          <t>1,37; 1,98</t>
         </is>
       </c>
     </row>
@@ -1696,37 +1696,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,09</t>
+          <t>1,45; 3,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,85</t>
+          <t>1,22; 2,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,87</t>
+          <t>1,31; 2,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,66</t>
+          <t>1,0; 1,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,4</t>
+          <t>1,45; 2,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,47</t>
+          <t>1,31; 3,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,68</t>
+          <t>1,16; 1,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1736,22 +1736,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,44</t>
+          <t>1,52; 2,4</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,76</t>
+          <t>1,4; 2,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,03</t>
+          <t>1,27; 2,03</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,31</t>
+          <t>1,0; 1,25</t>
         </is>
       </c>
     </row>
@@ -1836,22 +1836,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,79</t>
+          <t>1,41; 1,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,28</t>
+          <t>1,73; 2,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,32</t>
+          <t>1,69; 2,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,19</t>
+          <t>1,56; 2,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,85</t>
+          <t>1,52; 1,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,11</t>
+          <t>1,62; 2,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1881,17 +1881,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,95</t>
+          <t>1,67; 1,97</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,13</t>
+          <t>1,72; 2,12</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,09</t>
+          <t>1,66; 2,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Provincia-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,02</t>
+          <t>1,51; 4,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,92</t>
+          <t>1,94; 4,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,38</t>
+          <t>1,47; 2,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,73</t>
+          <t>1,7; 2,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,7</t>
+          <t>1,61; 2,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,66</t>
+          <t>1,61; 2,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,18</t>
+          <t>1,67; 3,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,1</t>
+          <t>1,63; 3,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,89</t>
+          <t>1,71; 2,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,02</t>
+          <t>1,85; 3,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,53</t>
+          <t>1,68; 2,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,61</t>
+          <t>1,74; 2,63</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,5</t>
+          <t>1,12; 1,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,4</t>
+          <t>1,66; 3,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,12</t>
+          <t>1,59; 2,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,41</t>
+          <t>1,64; 4,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 1,92</t>
+          <t>1,4; 1,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,19</t>
+          <t>1,34; 2,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,98</t>
+          <t>1,38; 1,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,07</t>
+          <t>1,49; 3,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,66</t>
+          <t>1,32; 1,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,46</t>
+          <t>1,57; 2,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,95</t>
+          <t>1,53; 1,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,46</t>
+          <t>1,74; 3,33</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,28</t>
+          <t>1,21; 2,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,78</t>
+          <t>1,56; 2,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,63</t>
+          <t>1,13; 2,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,71</t>
+          <t>1,14; 1,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1036,22 +1036,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,74</t>
+          <t>1,22; 1,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,13</t>
+          <t>1,44; 2,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,17</t>
+          <t>1,1; 2,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,12</t>
+          <t>1,15; 2,08</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,88</t>
+          <t>1,23; 1,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,09</t>
+          <t>1,91; 4,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,24</t>
+          <t>1,65; 3,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,21</t>
+          <t>1,29; 3,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,55</t>
+          <t>1,43; 2,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,81</t>
+          <t>1,49; 2,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,03</t>
+          <t>1,81; 3,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,66</t>
+          <t>1,46; 4,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,12</t>
+          <t>1,39; 2,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,01</t>
+          <t>1,81; 2,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,85</t>
+          <t>1,85; 2,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,2</t>
+          <t>1,54; 3,38</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,69</t>
+          <t>1,21; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,19</t>
+          <t>1,0; 2,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,86</t>
+          <t>1,13; 2,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,57</t>
+          <t>1,57; 2,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1316,22 +1316,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,35</t>
+          <t>1,29; 2,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 1,96</t>
+          <t>1,43; 1,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,9</t>
+          <t>1,1; 2,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,04</t>
+          <t>1,0; 1,99</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,62</t>
+          <t>1,0; 1,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,65</t>
+          <t>1,17; 1,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,64</t>
+          <t>1,43; 6,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,27 +1436,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,63</t>
+          <t>1,14; 1,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,42</t>
+          <t>1,04; 1,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,44</t>
+          <t>1,16; 3,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,19</t>
+          <t>1,28; 4,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,48</t>
+          <t>1,12; 1,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,24</t>
+          <t>1,46; 4,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,85</t>
+          <t>1,16; 2,95</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,64</t>
+          <t>1,21; 1,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,58</t>
+          <t>1,19; 1,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,11</t>
+          <t>1,24; 2,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,22</t>
+          <t>1,21; 2,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,99</t>
+          <t>1,3; 1,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,0</t>
+          <t>1,35; 2,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,71</t>
+          <t>1,17; 1,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,17</t>
+          <t>1,33; 2,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,69</t>
+          <t>1,33; 1,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,73</t>
+          <t>1,33; 1,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,82</t>
+          <t>1,28; 1,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,98</t>
+          <t>1,36; 1,99</t>
         </is>
       </c>
     </row>
@@ -1696,37 +1696,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,22</t>
+          <t>1,45; 3,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,84</t>
+          <t>1,23; 2,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,78</t>
+          <t>1,34; 3,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,59</t>
+          <t>1,0; 1,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,34</t>
+          <t>1,42; 2,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,77</t>
+          <t>1,36; 3,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,74</t>
+          <t>1,16; 1,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1736,22 +1736,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,4</t>
+          <t>1,54; 2,41</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,73</t>
+          <t>1,39; 2,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,03</t>
+          <t>1,3; 2,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,25</t>
+          <t>1,0; 1,3</t>
         </is>
       </c>
     </row>
@@ -1836,37 +1836,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,78</t>
+          <t>1,42; 1,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,29</t>
+          <t>1,73; 2,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,34</t>
+          <t>1,68; 2,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,2</t>
+          <t>1,61; 2,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,82</t>
+          <t>1,51; 1,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,86</t>
+          <t>1,53; 1,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,13</t>
+          <t>1,61; 2,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1876,22 +1876,22 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,75</t>
+          <t>1,51; 1,74</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,97</t>
+          <t>1,67; 1,95</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,12</t>
+          <t>1,74; 2,13</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,07</t>
+          <t>1,67; 2,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,02</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,81</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2,06</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,26</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,0</t>
+          <t>1,62; 2,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,83</t>
+          <t>1,61; 2,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,31</t>
+          <t>1,64; 3,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,79</t>
+          <t>1,62; 3,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,62</t>
+          <t>1,53; 3,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,73</t>
+          <t>1,99; 4,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,28</t>
+          <t>1,41; 2,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,05</t>
+          <t>1,61; 3,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,81</t>
+          <t>1,71; 2,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,2</t>
+          <t>1,86; 3,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,57</t>
+          <t>1,66; 2,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,63</t>
+          <t>1,74; 2,62</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,62</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,62</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,07</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,27</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,86</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2,36</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,48</t>
+          <t>1,4; 1,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,28</t>
+          <t>1,27; 2,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,1</t>
+          <t>1,38; 1,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,82</t>
+          <t>1,41; 2,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,93</t>
+          <t>1,15; 1,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,27</t>
+          <t>1,66; 3,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,96</t>
+          <t>1,62; 2,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,09</t>
+          <t>1,66; 4,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,65</t>
+          <t>1,32; 1,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,43</t>
+          <t>1,59; 2,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,93</t>
+          <t>1,54; 1,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,33</t>
+          <t>1,72; 3,47</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,36</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,38</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,58</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,04</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,68</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,24</t>
+          <t>1,08; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,91</t>
+          <t>1,16; 1,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,41</t>
+          <t>1,0; 2,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,52</t>
+          <t>1,24; 2,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,73</t>
+          <t>1,58; 2,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,14; 2,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,23</t>
+          <t>1,07; 2,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,76</t>
+          <t>1,2; 1,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,09</t>
+          <t>1,4; 2,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,08</t>
+          <t>1,09; 2,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,08</t>
+          <t>1,16; 2,05</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,87</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,37</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,48</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,69</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,23</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>2,09</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,88</t>
+          <t>1,42; 2,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,23</t>
+          <t>1,5; 2,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,31</t>
+          <t>1,84; 3,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,11</t>
+          <t>1,36; 4,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,63</t>
+          <t>1,23; 1,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,77</t>
+          <t>1,87; 4,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,2</t>
+          <t>1,62; 3,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,79</t>
+          <t>1,29; 2,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,1</t>
+          <t>1,42; 2,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,99</t>
+          <t>1,81; 2,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,88</t>
+          <t>1,89; 2,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,38</t>
+          <t>1,5; 3,06</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,98</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,95</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,42</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>1,99</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,35</t>
         </is>
       </c>
     </row>
@@ -1276,57 +1276,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,69</t>
+          <t>1,13; 2,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,71</t>
+          <t>1,57; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,94</t>
+          <t>1,0; 3,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,87</t>
+          <t>1,11; 2,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,53</t>
+          <t>1,19; 1,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,0; 2,85</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1,0; 3,0</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,41</t>
+          <t>1,35; 2,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 1,98</t>
+          <t>1,44; 1,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,78</t>
+          <t>1,1; 2,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1348,44 +1348,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,77</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1,37</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,77</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2,2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1,25</t>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,63</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,54</t>
+          <t>1,15; 1,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,68</t>
+          <t>1,04; 1,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,77</t>
+          <t>1,17; 3,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>1,28; 3,96</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 1,56</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1,18; 1,66</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1,43; 6,14</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 1,65</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,04; 1,43</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,16; 3,62</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 4,06</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,46</t>
+          <t>1,1; 1,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,43</t>
+          <t>1,14; 1,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,06</t>
+          <t>1,49; 4,68</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,95</t>
+          <t>1,17; 2,79</t>
         </is>
       </c>
     </row>
@@ -1488,62 +1488,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,58</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1,64</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1,38</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,35</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,51</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1,46</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,58</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,63</t>
+          <t>1,3; 1,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,6</t>
+          <t>1,35; 2,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,13</t>
+          <t>1,17; 1,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,26</t>
+          <t>1,33; 2,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,99</t>
+          <t>1,21; 1,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,04</t>
+          <t>1,19; 1,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,67</t>
+          <t>1,23; 2,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,17</t>
+          <t>1,18; 2,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,72</t>
+          <t>1,31; 1,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,72</t>
+          <t>1,34; 1,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,8</t>
+          <t>1,27; 1,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,99</t>
+          <t>1,32; 1,93</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>1,97</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1,74</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>1,85</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,34</t>
+          <t>1,42; 2,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,85</t>
+          <t>1,32; 3,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,07</t>
+          <t>1,14; 1,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,32</t>
+          <t>1,41; 3,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,57</t>
+          <t>1,18; 2,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,69</t>
+          <t>1,29; 2,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,0; 1,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,41</t>
+          <t>1,53; 2,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,73</t>
+          <t>1,46; 2,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,0</t>
+          <t>1,3; 2,03</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,3</t>
+          <t>1,0; 1,29</t>
         </is>
       </c>
     </row>
@@ -1768,62 +1768,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,65</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,83</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1,84</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1,56</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1,95</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,92</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,82</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
         </is>
       </c>
     </row>
@@ -1836,47 +1836,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,8</t>
+          <t>1,52; 1,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,27</t>
+          <t>1,53; 1,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,33</t>
+          <t>1,63; 2,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,2</t>
+          <t>1,59; 2,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,81</t>
+          <t>1,4; 1,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,87</t>
+          <t>1,72; 2,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,13</t>
+          <t>1,71; 2,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,21</t>
+          <t>1,54; 2,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,74</t>
+          <t>1,51; 1,75</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,13</t>
+          <t>1,72; 2,13</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,09</t>
+          <t>1,63; 2,05</t>
         </is>
       </c>
     </row>
